--- a/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold_generic/reinforcement_learning/mol2mol_scaffold_generic_rl_generated_optimal.xlsx
+++ b/outputs/generated/nitro_bioisostere_campaign/mol2mol_scaffold_generic/reinforcement_learning/mol2mol_scaffold_generic_rl_generated_optimal.xlsx
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="AA2" s="3">
-        <v>54.03302001953125</v>
+        <v>54.03302</v>
       </c>
       <c r="AB2" s="3">
-        <v>51.58975982666016</v>
+        <v>51.58976</v>
       </c>
       <c r="AC2" s="3">
-        <v>46.11929321289062</v>
+        <v>46.119293</v>
       </c>
       <c r="AD2" s="3">
         <v>0</v>
@@ -1589,55 +1589,55 @@
         <v>0</v>
       </c>
       <c r="AG2" s="3">
-        <v>0.1514938771724701</v>
+        <v>0.15149388</v>
       </c>
       <c r="AH2" s="3">
-        <v>0.3794129490852356</v>
+        <v>0.37941295</v>
       </c>
       <c r="AI2" s="3">
-        <v>0.790505588054657</v>
+        <v>0.7905056</v>
       </c>
       <c r="AJ2" s="3">
-        <v>0.05281468480825424</v>
+        <v>0.052814685</v>
       </c>
       <c r="AK2" s="3">
-        <v>0.8946078419685364</v>
+        <v>0.89460784</v>
       </c>
       <c r="AL2" s="3">
-        <v>0.4100111424922943</v>
+        <v>0.41001114</v>
       </c>
       <c r="AM2" s="3">
-        <v>0.6163969039916992</v>
+        <v>0.6163969</v>
       </c>
       <c r="AN2" s="3">
-        <v>0.7340325117111206</v>
+        <v>0.7340325</v>
       </c>
       <c r="AO2" s="3">
-        <v>0.2590197920799255</v>
+        <v>0.2590198</v>
       </c>
       <c r="AP2" s="3">
-        <v>0.9837437868118286</v>
+        <v>0.9837437999999999</v>
       </c>
       <c r="AQ2" s="3">
-        <v>0.9999759793281555</v>
+        <v>0.999976</v>
       </c>
       <c r="AR2" s="3">
-        <v>0.7540546655654907</v>
+        <v>0.75405467</v>
       </c>
       <c r="AS2" s="3">
-        <v>0.9556649327278137</v>
+        <v>0.95566493</v>
       </c>
       <c r="AT2" s="3">
-        <v>0.8375112414360046</v>
+        <v>0.83751124</v>
       </c>
       <c r="AU2" s="3">
-        <v>-4.578262329101562</v>
+        <v>-4.5782623</v>
       </c>
       <c r="AV2" s="3">
-        <v>98.41603851318359</v>
+        <v>98.41604</v>
       </c>
       <c r="AW2" s="3">
-        <v>6.461910247802734</v>
+        <v>6.4619102</v>
       </c>
       <c r="AX2" s="3">
         <v>421.4720000000002</v>
@@ -1708,7 +1708,7 @@
         <v>1.149479877483226</v>
       </c>
       <c r="M3" s="3">
-        <v>0.3450623085150972</v>
+        <v>0.3450623085150971</v>
       </c>
       <c r="N3" s="3">
         <v>18.23568173690457</v>
@@ -1720,7 +1720,7 @@
         <v>4.850520122516775</v>
       </c>
       <c r="Q3" s="3">
-        <v>0.3450623085150972</v>
+        <v>0.3450623085150971</v>
       </c>
       <c r="R3" s="3">
         <v>2.972745653490808</v>
@@ -1735,7 +1735,7 @@
         <v>5.526842247206365</v>
       </c>
       <c r="V3" s="3">
-        <v>0.3450623085150972</v>
+        <v>0.3450623085150971</v>
       </c>
       <c r="W3" s="3">
         <v>3.340300000000002</v>
@@ -1752,13 +1752,13 @@
         </is>
       </c>
       <c r="AA3" s="3">
-        <v>17.29001045227051</v>
+        <v>17.29001</v>
       </c>
       <c r="AB3" s="3">
-        <v>15.31085777282715</v>
+        <v>15.310858</v>
       </c>
       <c r="AC3" s="3">
-        <v>44.33369445800781</v>
+        <v>44.333694</v>
       </c>
       <c r="AD3" s="3">
         <v>0</v>
@@ -1770,55 +1770,55 @@
         <v>0</v>
       </c>
       <c r="AG3" s="3">
-        <v>0.09502832591533661</v>
+        <v>0.095028326</v>
       </c>
       <c r="AH3" s="3">
-        <v>0.6311066746711731</v>
+        <v>0.6311067</v>
       </c>
       <c r="AI3" s="3">
-        <v>0.6507071256637573</v>
+        <v>0.6507071</v>
       </c>
       <c r="AJ3" s="3">
-        <v>0.06331317126750946</v>
+        <v>0.06331317</v>
       </c>
       <c r="AK3" s="3">
-        <v>0.9500176310539246</v>
+        <v>0.9500176299999999</v>
       </c>
       <c r="AL3" s="3">
-        <v>0.1551773250102997</v>
+        <v>0.15517733</v>
       </c>
       <c r="AM3" s="3">
-        <v>0.2128761261701584</v>
+        <v>0.21287613</v>
       </c>
       <c r="AN3" s="3">
-        <v>0.3841579258441925</v>
+        <v>0.38415793</v>
       </c>
       <c r="AO3" s="3">
-        <v>0.3050800561904907</v>
+        <v>0.30508006</v>
       </c>
       <c r="AP3" s="3">
-        <v>0.9501555562019348</v>
+        <v>0.95015556</v>
       </c>
       <c r="AQ3" s="3">
-        <v>0.9998467564582825</v>
+        <v>0.9998467599999999</v>
       </c>
       <c r="AR3" s="3">
-        <v>0.8466672897338867</v>
+        <v>0.8466673</v>
       </c>
       <c r="AS3" s="3">
-        <v>0.9501722455024719</v>
+        <v>0.9501722500000001</v>
       </c>
       <c r="AT3" s="3">
-        <v>0.840124249458313</v>
+        <v>0.84012425</v>
       </c>
       <c r="AU3" s="3">
-        <v>-5.109377861022949</v>
+        <v>-5.109378</v>
       </c>
       <c r="AV3" s="3">
-        <v>92.88607025146484</v>
+        <v>92.88607</v>
       </c>
       <c r="AW3" s="3">
-        <v>11.60473537445068</v>
+        <v>11.604735</v>
       </c>
       <c r="AX3" s="3">
         <v>460.5000000000003</v>
@@ -1889,7 +1889,7 @@
         <v>1.036432393764884</v>
       </c>
       <c r="M4" s="3">
-        <v>0.3490444296987597</v>
+        <v>0.3490444296987596</v>
       </c>
       <c r="N4" s="3">
         <v>14.72258846820145</v>
@@ -1901,7 +1901,7 @@
         <v>4.963567606235117</v>
       </c>
       <c r="Q4" s="3">
-        <v>0.3490444296987597</v>
+        <v>0.3490444296987596</v>
       </c>
       <c r="R4" s="3">
         <v>2.250636260240134</v>
@@ -1916,7 +1916,7 @@
         <v>5.647694688444686</v>
       </c>
       <c r="V4" s="3">
-        <v>0.3490444296987597</v>
+        <v>0.3490444296987596</v>
       </c>
       <c r="W4" s="3">
         <v>3.395520000000002</v>
@@ -1933,13 +1933,13 @@
         </is>
       </c>
       <c r="AA4" s="3">
-        <v>19.92925453186035</v>
+        <v>19.929255</v>
       </c>
       <c r="AB4" s="3">
-        <v>18.81597518920898</v>
+        <v>18.815975</v>
       </c>
       <c r="AC4" s="3">
-        <v>40.82208633422852</v>
+        <v>40.822086</v>
       </c>
       <c r="AD4" s="3">
         <v>0</v>
@@ -1951,55 +1951,55 @@
         <v>0</v>
       </c>
       <c r="AG4" s="3">
-        <v>0.4004833102226257</v>
+        <v>0.4004833</v>
       </c>
       <c r="AH4" s="3">
-        <v>0.6817606687545776</v>
+        <v>0.68176067</v>
       </c>
       <c r="AI4" s="3">
-        <v>0.4466834962368011</v>
+        <v>0.4466835</v>
       </c>
       <c r="AJ4" s="3">
-        <v>0.05532924085855484</v>
+        <v>0.05532924</v>
       </c>
       <c r="AK4" s="3">
-        <v>0.9214924573898315</v>
+        <v>0.92149246</v>
       </c>
       <c r="AL4" s="3">
-        <v>0.05668352916836739</v>
+        <v>0.05668353</v>
       </c>
       <c r="AM4" s="3">
-        <v>0.0586969256401062</v>
+        <v>0.058696926</v>
       </c>
       <c r="AN4" s="3">
-        <v>0.0346602275967598</v>
+        <v>0.034660228</v>
       </c>
       <c r="AO4" s="3">
-        <v>0.4026454985141754</v>
+        <v>0.4026455</v>
       </c>
       <c r="AP4" s="3">
-        <v>0.7616280317306519</v>
+        <v>0.76162803</v>
       </c>
       <c r="AQ4" s="3">
-        <v>0.9993757009506226</v>
+        <v>0.9993757</v>
       </c>
       <c r="AR4" s="3">
-        <v>0.8266555070877075</v>
+        <v>0.8266555</v>
       </c>
       <c r="AS4" s="3">
-        <v>0.8858360052108765</v>
+        <v>0.885836</v>
       </c>
       <c r="AT4" s="3">
-        <v>0.4549710154533386</v>
+        <v>0.45497102</v>
       </c>
       <c r="AU4" s="3">
-        <v>-4.71553373336792</v>
+        <v>-4.7155337</v>
       </c>
       <c r="AV4" s="3">
-        <v>89.19620513916016</v>
+        <v>89.19620500000001</v>
       </c>
       <c r="AW4" s="3">
-        <v>7.42531681060791</v>
+        <v>7.425317</v>
       </c>
       <c r="AX4" s="3">
         <v>453.4890000000001</v>
@@ -2070,7 +2070,7 @@
         <v>1.142734159585373</v>
       </c>
       <c r="M5" s="3">
-        <v>0.3490890461207664</v>
+        <v>0.3490890461207663</v>
       </c>
       <c r="N5" s="3">
         <v>18.04324635783083</v>
@@ -2082,7 +2082,7 @@
         <v>4.857265840414628</v>
       </c>
       <c r="Q5" s="3">
-        <v>0.3490890461207664</v>
+        <v>0.3490890461207663</v>
       </c>
       <c r="R5" s="3">
         <v>2.874217499208906</v>
@@ -2097,7 +2097,7 @@
         <v>5.541480370811329</v>
       </c>
       <c r="V5" s="3">
-        <v>0.3490890461207664</v>
+        <v>0.3490890461207663</v>
       </c>
       <c r="W5" s="3">
         <v>2.81188</v>
@@ -2114,13 +2114,13 @@
         </is>
       </c>
       <c r="AA5" s="3">
-        <v>38.43938446044922</v>
+        <v>38.439384</v>
       </c>
       <c r="AB5" s="3">
-        <v>39.73931121826172</v>
+        <v>39.73931</v>
       </c>
       <c r="AC5" s="3">
-        <v>43.55910491943359</v>
+        <v>43.559105</v>
       </c>
       <c r="AD5" s="3">
         <v>0</v>
@@ -2132,55 +2132,55 @@
         <v>0</v>
       </c>
       <c r="AG5" s="3">
-        <v>0.3114796280860901</v>
+        <v>0.31147963</v>
       </c>
       <c r="AH5" s="3">
-        <v>0.2676551938056946</v>
+        <v>0.2676552</v>
       </c>
       <c r="AI5" s="3">
-        <v>0.8770459890365601</v>
+        <v>0.877046</v>
       </c>
       <c r="AJ5" s="3">
-        <v>0.08820271492004395</v>
+        <v>0.088202715</v>
       </c>
       <c r="AK5" s="3">
-        <v>0.7218542695045471</v>
+        <v>0.72185427</v>
       </c>
       <c r="AL5" s="3">
-        <v>0.08923223614692688</v>
+        <v>0.08923223600000001</v>
       </c>
       <c r="AM5" s="3">
-        <v>0.3359166383743286</v>
+        <v>0.33591664</v>
       </c>
       <c r="AN5" s="3">
-        <v>0.5657344460487366</v>
+        <v>0.56573445</v>
       </c>
       <c r="AO5" s="3">
-        <v>0.1457182765007019</v>
+        <v>0.14571828</v>
       </c>
       <c r="AP5" s="3">
-        <v>0.9311483502388</v>
+        <v>0.93114835</v>
       </c>
       <c r="AQ5" s="3">
-        <v>0.9989749193191528</v>
+        <v>0.9989749</v>
       </c>
       <c r="AR5" s="3">
-        <v>0.6683424711227417</v>
+        <v>0.6683425</v>
       </c>
       <c r="AS5" s="3">
-        <v>0.8554390668869019</v>
+        <v>0.85543907</v>
       </c>
       <c r="AT5" s="3">
-        <v>0.8302897214889526</v>
+        <v>0.8302897</v>
       </c>
       <c r="AU5" s="3">
-        <v>-4.660964012145996</v>
+        <v>-4.660964</v>
       </c>
       <c r="AV5" s="3">
-        <v>94.86743927001953</v>
+        <v>94.86744</v>
       </c>
       <c r="AW5" s="3">
-        <v>7.427783012390137</v>
+        <v>7.427783</v>
       </c>
       <c r="AX5" s="3">
         <v>478.9360000000003</v>
@@ -2251,7 +2251,7 @@
         <v>1.161480055239186</v>
       </c>
       <c r="M6" s="3">
-        <v>0.3673371277884137</v>
+        <v>0.3673371277884136</v>
       </c>
       <c r="N6" s="3">
         <v>19.41153086168973</v>
@@ -2263,7 +2263,7 @@
         <v>4.838519944760813</v>
       </c>
       <c r="Q6" s="3">
-        <v>0.3673371277884137</v>
+        <v>0.3673371277884136</v>
       </c>
       <c r="R6" s="3">
         <v>2.763753367626965</v>
@@ -2278,7 +2278,7 @@
         <v>5.558500715226105</v>
       </c>
       <c r="V6" s="3">
-        <v>0.3673371277884137</v>
+        <v>0.3673371277884136</v>
       </c>
       <c r="W6" s="3">
         <v>2.42178</v>
@@ -2295,13 +2295,13 @@
         </is>
       </c>
       <c r="AA6" s="3">
-        <v>39.34511566162109</v>
+        <v>39.345116</v>
       </c>
       <c r="AB6" s="3">
-        <v>31.9589786529541</v>
+        <v>31.958979</v>
       </c>
       <c r="AC6" s="3">
-        <v>47.43580627441406</v>
+        <v>47.435806</v>
       </c>
       <c r="AD6" s="3">
         <v>0</v>
@@ -2313,55 +2313,55 @@
         <v>0</v>
       </c>
       <c r="AG6" s="3">
-        <v>0.2926822006702423</v>
+        <v>0.2926822</v>
       </c>
       <c r="AH6" s="3">
-        <v>0.2759555876255035</v>
+        <v>0.2759556</v>
       </c>
       <c r="AI6" s="3">
-        <v>0.892932116985321</v>
+        <v>0.8929321</v>
       </c>
       <c r="AJ6" s="3">
-        <v>0.1061321720480919</v>
+        <v>0.10613217</v>
       </c>
       <c r="AK6" s="3">
-        <v>0.7119634747505188</v>
+        <v>0.7119635</v>
       </c>
       <c r="AL6" s="3">
-        <v>0.1024753302335739</v>
+        <v>0.10247533</v>
       </c>
       <c r="AM6" s="3">
-        <v>0.3437635898590088</v>
+        <v>0.3437636</v>
       </c>
       <c r="AN6" s="3">
-        <v>0.6002227067947388</v>
+        <v>0.6002227</v>
       </c>
       <c r="AO6" s="3">
-        <v>0.1347735077142715</v>
+        <v>0.13477351</v>
       </c>
       <c r="AP6" s="3">
-        <v>0.9220315217971802</v>
+        <v>0.9220315</v>
       </c>
       <c r="AQ6" s="3">
-        <v>0.9984925985336304</v>
+        <v>0.9984926</v>
       </c>
       <c r="AR6" s="3">
-        <v>0.6976286768913269</v>
+        <v>0.6976287</v>
       </c>
       <c r="AS6" s="3">
-        <v>0.833319365978241</v>
+        <v>0.83331937</v>
       </c>
       <c r="AT6" s="3">
-        <v>0.8141576051712036</v>
+        <v>0.8141576</v>
       </c>
       <c r="AU6" s="3">
-        <v>-4.625099182128906</v>
+        <v>-4.625099</v>
       </c>
       <c r="AV6" s="3">
-        <v>93.63883972167969</v>
+        <v>93.63884</v>
       </c>
       <c r="AW6" s="3">
-        <v>7.111278533935547</v>
+        <v>7.1112785</v>
       </c>
       <c r="AX6" s="3">
         <v>464.9090000000002</v>
@@ -2468,7 +2468,7 @@
         <v>-5.417679817153729</v>
       </c>
       <c r="Y7" s="3">
-        <v>3.822259624104331E-06</v>
+        <v>3.822259624104332E-06</v>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
@@ -2476,13 +2476,13 @@
         </is>
       </c>
       <c r="AA7" s="3">
-        <v>11.53824329376221</v>
+        <v>11.538243</v>
       </c>
       <c r="AB7" s="3">
-        <v>8.560314178466797</v>
+        <v>8.560314</v>
       </c>
       <c r="AC7" s="3">
-        <v>50.547607421875</v>
+        <v>50.547607</v>
       </c>
       <c r="AD7" s="3">
         <v>0</v>
@@ -2494,55 +2494,55 @@
         <v>0</v>
       </c>
       <c r="AG7" s="3">
-        <v>0.1729737222194672</v>
+        <v>0.17297372</v>
       </c>
       <c r="AH7" s="3">
-        <v>0.7112715840339661</v>
+        <v>0.7112716</v>
       </c>
       <c r="AI7" s="3">
-        <v>0.6234567165374756</v>
+        <v>0.6234567</v>
       </c>
       <c r="AJ7" s="3">
-        <v>0.06960327923297882</v>
+        <v>0.06960328</v>
       </c>
       <c r="AK7" s="3">
-        <v>0.970696747303009</v>
+        <v>0.97069675</v>
       </c>
       <c r="AL7" s="3">
-        <v>0.29461270570755</v>
+        <v>0.2946127</v>
       </c>
       <c r="AM7" s="3">
-        <v>0.2502461671829224</v>
+        <v>0.25024617</v>
       </c>
       <c r="AN7" s="3">
-        <v>0.3388939499855042</v>
+        <v>0.33889395</v>
       </c>
       <c r="AO7" s="3">
-        <v>0.529526948928833</v>
+        <v>0.5295269500000001</v>
       </c>
       <c r="AP7" s="3">
-        <v>0.948264479637146</v>
+        <v>0.9482645</v>
       </c>
       <c r="AQ7" s="3">
-        <v>0.9997991323471069</v>
+        <v>0.99979913</v>
       </c>
       <c r="AR7" s="3">
-        <v>0.8182163238525391</v>
+        <v>0.8182163</v>
       </c>
       <c r="AS7" s="3">
-        <v>0.9356530904769897</v>
+        <v>0.9356531</v>
       </c>
       <c r="AT7" s="3">
-        <v>0.8393914103507996</v>
+        <v>0.8393914</v>
       </c>
       <c r="AU7" s="3">
-        <v>-5.35416316986084</v>
+        <v>-5.354163</v>
       </c>
       <c r="AV7" s="3">
-        <v>87.81090545654297</v>
+        <v>87.81090500000001</v>
       </c>
       <c r="AW7" s="3">
-        <v>15.94587135314941</v>
+        <v>15.945871</v>
       </c>
       <c r="AX7" s="3">
         <v>459.5160000000002</v>
@@ -2613,7 +2613,7 @@
         <v>1.21429464537239</v>
       </c>
       <c r="M8" s="3">
-        <v>0.3825573046960529</v>
+        <v>0.3825573046960528</v>
       </c>
       <c r="N8" s="3">
         <v>22.41973092789085</v>
@@ -2625,13 +2625,13 @@
         <v>4.78570535462761</v>
       </c>
       <c r="Q8" s="3">
-        <v>0.3825573046960529</v>
+        <v>0.3825573046960528</v>
       </c>
       <c r="R8" s="3">
         <v>2.913951561056608</v>
       </c>
       <c r="S8" s="3">
-        <v>92.06762975972009</v>
+        <v>92.06762975972008</v>
       </c>
       <c r="T8" s="3">
         <v>4.035893037423346</v>
@@ -2640,7 +2640,7 @@
         <v>5.535517671831873</v>
       </c>
       <c r="V8" s="3">
-        <v>0.3825573046960529</v>
+        <v>0.3825573046960528</v>
       </c>
       <c r="W8" s="3">
         <v>2.983300000000001</v>
@@ -2657,13 +2657,13 @@
         </is>
       </c>
       <c r="AA8" s="3">
-        <v>8.585546493530273</v>
+        <v>8.5855465</v>
       </c>
       <c r="AB8" s="3">
-        <v>-1.620642066001892</v>
+        <v>-1.6206421</v>
       </c>
       <c r="AC8" s="3">
-        <v>51.75014114379883</v>
+        <v>51.75014</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
@@ -2675,55 +2675,55 @@
         <v>0</v>
       </c>
       <c r="AG8" s="3">
-        <v>0.1352551877498627</v>
+        <v>0.13525519</v>
       </c>
       <c r="AH8" s="3">
-        <v>0.7002271413803101</v>
+        <v>0.70022714</v>
       </c>
       <c r="AI8" s="3">
-        <v>0.6512983441352844</v>
+        <v>0.65129834</v>
       </c>
       <c r="AJ8" s="3">
-        <v>0.07807555049657822</v>
+        <v>0.07807554999999999</v>
       </c>
       <c r="AK8" s="3">
-        <v>0.9641662836074829</v>
+        <v>0.9641663</v>
       </c>
       <c r="AL8" s="3">
-        <v>0.2838209271430969</v>
+        <v>0.28382093</v>
       </c>
       <c r="AM8" s="3">
-        <v>0.2409442961215973</v>
+        <v>0.2409443</v>
       </c>
       <c r="AN8" s="3">
-        <v>0.379910409450531</v>
+        <v>0.3799104</v>
       </c>
       <c r="AO8" s="3">
-        <v>0.4853502213954926</v>
+        <v>0.48535022</v>
       </c>
       <c r="AP8" s="3">
-        <v>0.9311615228652954</v>
+        <v>0.9311615</v>
       </c>
       <c r="AQ8" s="3">
-        <v>0.9997544288635254</v>
+        <v>0.9997544</v>
       </c>
       <c r="AR8" s="3">
-        <v>0.8442096710205078</v>
+        <v>0.8442097</v>
       </c>
       <c r="AS8" s="3">
-        <v>0.9253891706466675</v>
+        <v>0.9253892</v>
       </c>
       <c r="AT8" s="3">
-        <v>0.7999110817909241</v>
+        <v>0.7999111</v>
       </c>
       <c r="AU8" s="3">
-        <v>-5.303637981414795</v>
+        <v>-5.303638</v>
       </c>
       <c r="AV8" s="3">
-        <v>86.18064880371094</v>
+        <v>86.18065</v>
       </c>
       <c r="AW8" s="3">
-        <v>15.25523948669434</v>
+        <v>15.2552395</v>
       </c>
       <c r="AX8" s="3">
         <v>445.4890000000002</v>
@@ -2797,7 +2797,7 @@
         <v>0.3922932995004642</v>
       </c>
       <c r="N9" s="3">
-        <v>21.45408987995463</v>
+        <v>21.45408987995462</v>
       </c>
       <c r="O9" s="3">
         <v>15.05535990379625</v>
@@ -2838,13 +2838,13 @@
         </is>
       </c>
       <c r="AA9" s="3">
-        <v>15.32742786407471</v>
+        <v>15.327428</v>
       </c>
       <c r="AB9" s="3">
-        <v>5.395439624786377</v>
+        <v>5.3954396</v>
       </c>
       <c r="AC9" s="3">
-        <v>40.00891876220703</v>
+        <v>40.00892</v>
       </c>
       <c r="AD9" s="3">
         <v>0</v>
@@ -2856,55 +2856,55 @@
         <v>0</v>
       </c>
       <c r="AG9" s="3">
-        <v>0.265686422586441</v>
+        <v>0.26568642</v>
       </c>
       <c r="AH9" s="3">
-        <v>0.2258575409650803</v>
+        <v>0.22585754</v>
       </c>
       <c r="AI9" s="3">
-        <v>0.8297006487846375</v>
+        <v>0.82970065</v>
       </c>
       <c r="AJ9" s="3">
-        <v>0.07411851733922958</v>
+        <v>0.07411851999999999</v>
       </c>
       <c r="AK9" s="3">
-        <v>0.5354483723640442</v>
+        <v>0.5354484</v>
       </c>
       <c r="AL9" s="3">
-        <v>0.0353969931602478</v>
+        <v>0.035396993</v>
       </c>
       <c r="AM9" s="3">
-        <v>0.1424608528614044</v>
+        <v>0.14246085</v>
       </c>
       <c r="AN9" s="3">
-        <v>0.2378669083118439</v>
+        <v>0.23786691</v>
       </c>
       <c r="AO9" s="3">
-        <v>0.0317249484360218</v>
+        <v>0.03172495</v>
       </c>
       <c r="AP9" s="3">
-        <v>0.6754664182662964</v>
+        <v>0.6754664</v>
       </c>
       <c r="AQ9" s="3">
-        <v>0.9987910985946655</v>
+        <v>0.9987911</v>
       </c>
       <c r="AR9" s="3">
-        <v>0.8262612223625183</v>
+        <v>0.8262612</v>
       </c>
       <c r="AS9" s="3">
-        <v>0.8856707811355591</v>
+        <v>0.8856708</v>
       </c>
       <c r="AT9" s="3">
-        <v>0.6211746335029602</v>
+        <v>0.6211746299999999</v>
       </c>
       <c r="AU9" s="3">
-        <v>-4.586371898651123</v>
+        <v>-4.586372</v>
       </c>
       <c r="AV9" s="3">
-        <v>86.72911071777344</v>
+        <v>86.72911000000001</v>
       </c>
       <c r="AW9" s="3">
-        <v>6.039958000183105</v>
+        <v>6.039958</v>
       </c>
       <c r="AX9" s="3">
         <v>446.5260000000003</v>
@@ -2972,10 +2972,10 @@
         <v>5.442375258869468</v>
       </c>
       <c r="L10" s="3">
-        <v>0.9632181824737633</v>
+        <v>0.9632181824737632</v>
       </c>
       <c r="M10" s="3">
-        <v>0.345537765387931</v>
+        <v>0.3455377653879309</v>
       </c>
       <c r="N10" s="3">
         <v>12.85032918255135</v>
@@ -2987,7 +2987,7 @@
         <v>5.036781817526236</v>
       </c>
       <c r="Q10" s="3">
-        <v>0.345537765387931</v>
+        <v>0.3455377653879309</v>
       </c>
       <c r="R10" s="3">
         <v>1.931808898877189</v>
@@ -3002,7 +3002,7 @@
         <v>5.714035837686581</v>
       </c>
       <c r="V10" s="3">
-        <v>0.345537765387931</v>
+        <v>0.3455377653879309</v>
       </c>
       <c r="W10" s="3">
         <v>2.730700000000001</v>
@@ -3019,13 +3019,13 @@
         </is>
       </c>
       <c r="AA10" s="3">
-        <v>48.87473678588867</v>
+        <v>48.874737</v>
       </c>
       <c r="AB10" s="3">
-        <v>42.1167106628418</v>
+        <v>42.11671</v>
       </c>
       <c r="AC10" s="3">
-        <v>44.57409286499023</v>
+        <v>44.574093</v>
       </c>
       <c r="AD10" s="3">
         <v>0</v>
@@ -3037,55 +3037,55 @@
         <v>0</v>
       </c>
       <c r="AG10" s="3">
-        <v>0.2590630948543549</v>
+        <v>0.2590631</v>
       </c>
       <c r="AH10" s="3">
-        <v>0.3988601267337799</v>
+        <v>0.39886013</v>
       </c>
       <c r="AI10" s="3">
-        <v>0.7928101420402527</v>
+        <v>0.7928101400000001</v>
       </c>
       <c r="AJ10" s="3">
-        <v>0.03703287988901138</v>
+        <v>0.03703288</v>
       </c>
       <c r="AK10" s="3">
-        <v>0.7951525449752808</v>
+        <v>0.79515254</v>
       </c>
       <c r="AL10" s="3">
-        <v>0.09543224424123764</v>
+        <v>0.095432244</v>
       </c>
       <c r="AM10" s="3">
-        <v>0.1838532388210297</v>
+        <v>0.18385324</v>
       </c>
       <c r="AN10" s="3">
-        <v>0.2135164737701416</v>
+        <v>0.21351647</v>
       </c>
       <c r="AO10" s="3">
-        <v>0.05547567084431648</v>
+        <v>0.05547567</v>
       </c>
       <c r="AP10" s="3">
-        <v>0.8860576748847961</v>
+        <v>0.8860576999999999</v>
       </c>
       <c r="AQ10" s="3">
-        <v>0.9999348521232605</v>
+        <v>0.99993485</v>
       </c>
       <c r="AR10" s="3">
-        <v>0.8804370760917664</v>
+        <v>0.8804371</v>
       </c>
       <c r="AS10" s="3">
-        <v>0.9522743225097656</v>
+        <v>0.9522743</v>
       </c>
       <c r="AT10" s="3">
-        <v>0.5102437734603882</v>
+        <v>0.5102438</v>
       </c>
       <c r="AU10" s="3">
-        <v>-4.564610004425049</v>
+        <v>-4.56461</v>
       </c>
       <c r="AV10" s="3">
-        <v>92.37276458740234</v>
+        <v>92.372765</v>
       </c>
       <c r="AW10" s="3">
-        <v>6.734860420227051</v>
+        <v>6.7348604</v>
       </c>
       <c r="AX10" s="3">
         <v>406.4610000000002</v>
@@ -3186,7 +3186,7 @@
         <v>0.3938186041496197</v>
       </c>
       <c r="W11" s="3">
-        <v>3.052700000000002</v>
+        <v>3.052700000000001</v>
       </c>
       <c r="X11" s="3">
         <v>-4.926992101170115</v>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="AA11" s="3">
-        <v>24.94895935058594</v>
+        <v>24.94896</v>
       </c>
       <c r="AB11" s="3">
-        <v>2.014919996261597</v>
+        <v>2.01492</v>
       </c>
       <c r="AC11" s="3">
-        <v>41.75579071044922</v>
+        <v>41.75579</v>
       </c>
       <c r="AD11" s="3">
         <v>0</v>
@@ -3218,61 +3218,61 @@
         <v>0</v>
       </c>
       <c r="AG11" s="3">
-        <v>0.1191263347864151</v>
+        <v>0.119126335</v>
       </c>
       <c r="AH11" s="3">
-        <v>0.5101938843727112</v>
+        <v>0.5101939</v>
       </c>
       <c r="AI11" s="3">
-        <v>0.7018110156059265</v>
+        <v>0.701811</v>
       </c>
       <c r="AJ11" s="3">
-        <v>0.0970463752746582</v>
+        <v>0.097046375</v>
       </c>
       <c r="AK11" s="3">
-        <v>0.7446748018264771</v>
+        <v>0.7446748</v>
       </c>
       <c r="AL11" s="3">
-        <v>0.3749043941497803</v>
+        <v>0.3749044</v>
       </c>
       <c r="AM11" s="3">
-        <v>0.07624031603336334</v>
+        <v>0.076240316</v>
       </c>
       <c r="AN11" s="3">
-        <v>0.1046972721815109</v>
+        <v>0.10469727</v>
       </c>
       <c r="AO11" s="3">
-        <v>0.1270578056573868</v>
+        <v>0.1270578</v>
       </c>
       <c r="AP11" s="3">
-        <v>0.3602305352687836</v>
+        <v>0.36023054</v>
       </c>
       <c r="AQ11" s="3">
-        <v>0.9999613761901855</v>
+        <v>0.9999614</v>
       </c>
       <c r="AR11" s="3">
-        <v>0.958283543586731</v>
+        <v>0.95828354</v>
       </c>
       <c r="AS11" s="3">
-        <v>0.9795086979866028</v>
+        <v>0.9795087</v>
       </c>
       <c r="AT11" s="3">
-        <v>0.1666211932897568</v>
+        <v>0.1666212</v>
       </c>
       <c r="AU11" s="3">
-        <v>-4.870932579040527</v>
+        <v>-4.8709326</v>
       </c>
       <c r="AV11" s="3">
-        <v>84.90583801269531</v>
+        <v>84.90584</v>
       </c>
       <c r="AW11" s="3">
-        <v>6.139695644378662</v>
+        <v>6.1396956</v>
       </c>
       <c r="AX11" s="3">
         <v>418.4230000000001</v>
       </c>
       <c r="AY11" s="3">
-        <v>3.052700000000002</v>
+        <v>3.052700000000001</v>
       </c>
       <c r="AZ11" s="3">
         <v>0.7551931182087642</v>
@@ -3346,7 +3346,7 @@
         <v>76.0808612751983</v>
       </c>
       <c r="P12" s="3">
-        <v>4.797356000773195</v>
+        <v>4.797356000773196</v>
       </c>
       <c r="Q12" s="3">
         <v>0.6027867767415637</v>
@@ -3358,7 +3358,7 @@
         <v>242.1620484371657</v>
       </c>
       <c r="T12" s="3">
-        <v>3.61589391835973</v>
+        <v>3.615893918359729</v>
       </c>
       <c r="U12" s="3">
         <v>5.97881808318666</v>
@@ -3381,13 +3381,13 @@
         </is>
       </c>
       <c r="AA12" s="3">
-        <v>59.47089767456055</v>
+        <v>59.470898</v>
       </c>
       <c r="AB12" s="3">
-        <v>57.21720504760742</v>
+        <v>57.217205</v>
       </c>
       <c r="AC12" s="3">
-        <v>40.80253601074219</v>
+        <v>40.802536</v>
       </c>
       <c r="AD12" s="3">
         <v>0</v>
@@ -3399,55 +3399,55 @@
         <v>0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.1844686418771744</v>
+        <v>0.18446864</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.4202435612678528</v>
+        <v>0.42024356</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.8358316421508789</v>
+        <v>0.83583164</v>
       </c>
       <c r="AJ12" s="3">
-        <v>0.04515016451478004</v>
+        <v>0.045150165</v>
       </c>
       <c r="AK12" s="3">
-        <v>0.9386307001113892</v>
+        <v>0.9386307</v>
       </c>
       <c r="AL12" s="3">
-        <v>0.4181107878684998</v>
+        <v>0.4181108</v>
       </c>
       <c r="AM12" s="3">
-        <v>0.7442826628684998</v>
+        <v>0.74428266</v>
       </c>
       <c r="AN12" s="3">
-        <v>0.8617993593215942</v>
+        <v>0.86179936</v>
       </c>
       <c r="AO12" s="3">
-        <v>0.2975648641586304</v>
+        <v>0.29756486</v>
       </c>
       <c r="AP12" s="3">
-        <v>0.9936869740486145</v>
+        <v>0.993687</v>
       </c>
       <c r="AQ12" s="3">
-        <v>0.9999872446060181</v>
+        <v>0.9999872400000001</v>
       </c>
       <c r="AR12" s="3">
-        <v>0.7217900156974792</v>
+        <v>0.72179</v>
       </c>
       <c r="AS12" s="3">
-        <v>0.9570226669311523</v>
+        <v>0.95702267</v>
       </c>
       <c r="AT12" s="3">
-        <v>0.9055355191230774</v>
+        <v>0.9055355</v>
       </c>
       <c r="AU12" s="3">
-        <v>-4.767285823822021</v>
+        <v>-4.767286</v>
       </c>
       <c r="AV12" s="3">
-        <v>101.1879043579102</v>
+        <v>101.187904</v>
       </c>
       <c r="AW12" s="3">
-        <v>5.748510837554932</v>
+        <v>5.748511</v>
       </c>
       <c r="AX12" s="3">
         <v>432.5240000000002</v>
@@ -3554,7 +3554,7 @@
         <v>-4.63289378254872</v>
       </c>
       <c r="Y13" s="3">
-        <v>2.328660719567483E-05</v>
+        <v>2.328660719567484E-05</v>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
@@ -3562,13 +3562,13 @@
         </is>
       </c>
       <c r="AA13" s="3">
-        <v>45.45298385620117</v>
+        <v>45.452984</v>
       </c>
       <c r="AB13" s="3">
-        <v>45.61176681518555</v>
+        <v>45.611767</v>
       </c>
       <c r="AC13" s="3">
-        <v>42.49560546875</v>
+        <v>42.495605</v>
       </c>
       <c r="AD13" s="3">
         <v>0</v>
@@ -3580,55 +3580,55 @@
         <v>0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.1570702940225601</v>
+        <v>0.1570703</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.2612410485744476</v>
+        <v>0.26124105</v>
       </c>
       <c r="AI13" s="3">
-        <v>0.7992112040519714</v>
+        <v>0.7992112</v>
       </c>
       <c r="AJ13" s="3">
-        <v>0.03921898454427719</v>
+        <v>0.039218985</v>
       </c>
       <c r="AK13" s="3">
-        <v>0.6810072660446167</v>
+        <v>0.6810072700000001</v>
       </c>
       <c r="AL13" s="3">
-        <v>0.1737482398748398</v>
+        <v>0.17374824</v>
       </c>
       <c r="AM13" s="3">
-        <v>0.2636741995811462</v>
+        <v>0.2636742</v>
       </c>
       <c r="AN13" s="3">
-        <v>0.3221924901008606</v>
+        <v>0.3221925</v>
       </c>
       <c r="AO13" s="3">
-        <v>0.04175160080194473</v>
+        <v>0.0417516</v>
       </c>
       <c r="AP13" s="3">
-        <v>0.8595503568649292</v>
+        <v>0.85955036</v>
       </c>
       <c r="AQ13" s="3">
-        <v>0.9999492764472961</v>
+        <v>0.9999493</v>
       </c>
       <c r="AR13" s="3">
-        <v>0.8674739003181458</v>
+        <v>0.8674739</v>
       </c>
       <c r="AS13" s="3">
-        <v>0.9626019597053528</v>
+        <v>0.96260196</v>
       </c>
       <c r="AT13" s="3">
-        <v>0.5522476434707642</v>
+        <v>0.55224764</v>
       </c>
       <c r="AU13" s="3">
-        <v>-4.510308265686035</v>
+        <v>-4.5103083</v>
       </c>
       <c r="AV13" s="3">
-        <v>93.69382476806641</v>
+        <v>93.693825</v>
       </c>
       <c r="AW13" s="3">
-        <v>5.846985816955566</v>
+        <v>5.846986</v>
       </c>
       <c r="AX13" s="3">
         <v>391.4460000000002</v>
@@ -3720,7 +3720,7 @@
         <v>100.8861484082774</v>
       </c>
       <c r="T14" s="3">
-        <v>3.99616845797325</v>
+        <v>3.996168457973249</v>
       </c>
       <c r="U14" s="3">
         <v>5.597029499286857</v>
@@ -3732,7 +3732,7 @@
         <v>3.493100000000002</v>
       </c>
       <c r="X14" s="3">
-        <v>-5.349842559841663</v>
+        <v>-5.349842559841664</v>
       </c>
       <c r="Y14" s="3">
         <v>4.46845552956828E-06</v>
@@ -3743,13 +3743,13 @@
         </is>
       </c>
       <c r="AA14" s="3">
-        <v>48.53768157958984</v>
+        <v>48.53768</v>
       </c>
       <c r="AB14" s="3">
-        <v>39.91524124145508</v>
+        <v>39.91524</v>
       </c>
       <c r="AC14" s="3">
-        <v>44.43175888061523</v>
+        <v>44.43176</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -3761,55 +3761,55 @@
         <v>0</v>
       </c>
       <c r="AG14" s="3">
-        <v>0.1002922058105469</v>
+        <v>0.100292206</v>
       </c>
       <c r="AH14" s="3">
-        <v>0.3125008940696716</v>
+        <v>0.3125009</v>
       </c>
       <c r="AI14" s="3">
-        <v>0.8873043060302734</v>
+        <v>0.8873043</v>
       </c>
       <c r="AJ14" s="3">
-        <v>0.07599396258592606</v>
+        <v>0.07599396</v>
       </c>
       <c r="AK14" s="3">
-        <v>0.7342517375946045</v>
+        <v>0.73425174</v>
       </c>
       <c r="AL14" s="3">
-        <v>0.0499752089381218</v>
+        <v>0.04997521</v>
       </c>
       <c r="AM14" s="3">
-        <v>0.3700131475925446</v>
+        <v>0.37001315</v>
       </c>
       <c r="AN14" s="3">
-        <v>0.5537644624710083</v>
+        <v>0.55376446</v>
       </c>
       <c r="AO14" s="3">
-        <v>0.07810302823781967</v>
+        <v>0.07810303</v>
       </c>
       <c r="AP14" s="3">
-        <v>0.8581870198249817</v>
+        <v>0.858187</v>
       </c>
       <c r="AQ14" s="3">
-        <v>0.9993387460708618</v>
+        <v>0.9993387500000001</v>
       </c>
       <c r="AR14" s="3">
-        <v>0.7794610261917114</v>
+        <v>0.779461</v>
       </c>
       <c r="AS14" s="3">
-        <v>0.8544185757637024</v>
+        <v>0.8544186</v>
       </c>
       <c r="AT14" s="3">
-        <v>0.6763629913330078</v>
+        <v>0.676363</v>
       </c>
       <c r="AU14" s="3">
-        <v>-5.125014781951904</v>
+        <v>-5.125015</v>
       </c>
       <c r="AV14" s="3">
-        <v>100.9947738647461</v>
+        <v>100.994774</v>
       </c>
       <c r="AW14" s="3">
-        <v>6.518463134765625</v>
+        <v>6.518463</v>
       </c>
       <c r="AX14" s="3">
         <v>428.5400000000001</v>
@@ -3895,7 +3895,7 @@
         <v>0.3190053594260588</v>
       </c>
       <c r="R15" s="3">
-        <v>3.669747000929191</v>
+        <v>3.669747000929192</v>
       </c>
       <c r="S15" s="3">
         <v>65.33368182447869</v>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="AA15" s="3">
-        <v>14.75351905822754</v>
+        <v>14.753519</v>
       </c>
       <c r="AB15" s="3">
-        <v>6.042529106140137</v>
+        <v>6.042529</v>
       </c>
       <c r="AC15" s="3">
-        <v>47.24015426635742</v>
+        <v>47.240154</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -3942,55 +3942,55 @@
         <v>0</v>
       </c>
       <c r="AG15" s="3">
-        <v>0.07038719952106476</v>
+        <v>0.0703872</v>
       </c>
       <c r="AH15" s="3">
-        <v>0.6108044385910034</v>
+        <v>0.61080444</v>
       </c>
       <c r="AI15" s="3">
-        <v>0.686252772808075</v>
+        <v>0.6862528</v>
       </c>
       <c r="AJ15" s="3">
-        <v>0.07403627783060074</v>
+        <v>0.07403628</v>
       </c>
       <c r="AK15" s="3">
-        <v>0.9364877939224243</v>
+        <v>0.9364878</v>
       </c>
       <c r="AL15" s="3">
-        <v>0.1502557694911957</v>
+        <v>0.15025577</v>
       </c>
       <c r="AM15" s="3">
-        <v>0.2028278857469559</v>
+        <v>0.20282789</v>
       </c>
       <c r="AN15" s="3">
-        <v>0.4327522218227386</v>
+        <v>0.43275222</v>
       </c>
       <c r="AO15" s="3">
-        <v>0.2557015717029572</v>
+        <v>0.25570157</v>
       </c>
       <c r="AP15" s="3">
-        <v>0.9282855987548828</v>
+        <v>0.9282856</v>
       </c>
       <c r="AQ15" s="3">
-        <v>0.9998404383659363</v>
+        <v>0.9998404400000001</v>
       </c>
       <c r="AR15" s="3">
-        <v>0.8732077479362488</v>
+        <v>0.8732077499999999</v>
       </c>
       <c r="AS15" s="3">
-        <v>0.9415786862373352</v>
+        <v>0.9415787</v>
       </c>
       <c r="AT15" s="3">
-        <v>0.7919232845306396</v>
+        <v>0.7919233</v>
       </c>
       <c r="AU15" s="3">
-        <v>-5.061132431030273</v>
+        <v>-5.0611324</v>
       </c>
       <c r="AV15" s="3">
-        <v>91.65956878662109</v>
+        <v>91.65957</v>
       </c>
       <c r="AW15" s="3">
-        <v>11.25568103790283</v>
+        <v>11.255681</v>
       </c>
       <c r="AX15" s="3">
         <v>446.4730000000002</v>
@@ -4067,7 +4067,7 @@
         <v>20.39624186267761</v>
       </c>
       <c r="O16" s="3">
-        <v>13.11368351337333</v>
+        <v>13.11368351337334</v>
       </c>
       <c r="P16" s="3">
         <v>4.807671219231117</v>
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="AA16" s="3">
-        <v>30.9177131652832</v>
+        <v>30.917713</v>
       </c>
       <c r="AB16" s="3">
-        <v>35.26760864257812</v>
+        <v>35.26761</v>
       </c>
       <c r="AC16" s="3">
-        <v>50.92921447753906</v>
+        <v>50.929214</v>
       </c>
       <c r="AD16" s="3">
         <v>0</v>
@@ -4123,55 +4123,55 @@
         <v>0</v>
       </c>
       <c r="AG16" s="3">
-        <v>0.300019383430481</v>
+        <v>0.30001938</v>
       </c>
       <c r="AH16" s="3">
-        <v>0.2547107040882111</v>
+        <v>0.2547107</v>
       </c>
       <c r="AI16" s="3">
-        <v>0.8733264207839966</v>
+        <v>0.8733263999999999</v>
       </c>
       <c r="AJ16" s="3">
-        <v>0.08236296474933624</v>
+        <v>0.082362965</v>
       </c>
       <c r="AK16" s="3">
-        <v>0.7440570592880249</v>
+        <v>0.74405706</v>
       </c>
       <c r="AL16" s="3">
-        <v>0.08698789030313492</v>
+        <v>0.08698789</v>
       </c>
       <c r="AM16" s="3">
-        <v>0.3862351775169373</v>
+        <v>0.38623518</v>
       </c>
       <c r="AN16" s="3">
-        <v>0.6220148801803589</v>
+        <v>0.6220149</v>
       </c>
       <c r="AO16" s="3">
-        <v>0.1492623686790466</v>
+        <v>0.14926237</v>
       </c>
       <c r="AP16" s="3">
-        <v>0.9491135478019714</v>
+        <v>0.94911355</v>
       </c>
       <c r="AQ16" s="3">
-        <v>0.9993950724601746</v>
+        <v>0.9993951</v>
       </c>
       <c r="AR16" s="3">
-        <v>0.6402009725570679</v>
+        <v>0.640201</v>
       </c>
       <c r="AS16" s="3">
-        <v>0.8719772100448608</v>
+        <v>0.8719772</v>
       </c>
       <c r="AT16" s="3">
-        <v>0.8641490936279297</v>
+        <v>0.8641491</v>
       </c>
       <c r="AU16" s="3">
-        <v>-4.663098812103271</v>
+        <v>-4.663099</v>
       </c>
       <c r="AV16" s="3">
-        <v>96.55876159667969</v>
+        <v>96.55876000000001</v>
       </c>
       <c r="AW16" s="3">
-        <v>8.227945327758789</v>
+        <v>8.227945</v>
       </c>
       <c r="AX16" s="3">
         <v>492.9630000000003</v>
@@ -4286,13 +4286,13 @@
         </is>
       </c>
       <c r="AA17" s="3">
-        <v>37.09872436523438</v>
+        <v>37.098724</v>
       </c>
       <c r="AB17" s="3">
-        <v>27.07161331176758</v>
+        <v>27.071613</v>
       </c>
       <c r="AC17" s="3">
-        <v>52.21378707885742</v>
+        <v>52.213787</v>
       </c>
       <c r="AD17" s="3">
         <v>0</v>
@@ -4304,55 +4304,55 @@
         <v>0</v>
       </c>
       <c r="AG17" s="3">
-        <v>0.2416284531354904</v>
+        <v>0.24162845</v>
       </c>
       <c r="AH17" s="3">
-        <v>0.3985059559345245</v>
+        <v>0.39850596</v>
       </c>
       <c r="AI17" s="3">
-        <v>0.8635267019271851</v>
+        <v>0.8635267</v>
       </c>
       <c r="AJ17" s="3">
-        <v>0.07965370267629623</v>
+        <v>0.07965369999999999</v>
       </c>
       <c r="AK17" s="3">
-        <v>0.7850184440612793</v>
+        <v>0.78501844</v>
       </c>
       <c r="AL17" s="3">
-        <v>0.07722991704940796</v>
+        <v>0.07722991999999999</v>
       </c>
       <c r="AM17" s="3">
-        <v>0.3110678493976593</v>
+        <v>0.31106785</v>
       </c>
       <c r="AN17" s="3">
-        <v>0.4326716959476471</v>
+        <v>0.4326717</v>
       </c>
       <c r="AO17" s="3">
-        <v>0.1062991768121719</v>
+        <v>0.10629918</v>
       </c>
       <c r="AP17" s="3">
-        <v>0.8179564476013184</v>
+        <v>0.8179564499999999</v>
       </c>
       <c r="AQ17" s="3">
-        <v>0.9985162615776062</v>
+        <v>0.99851626</v>
       </c>
       <c r="AR17" s="3">
-        <v>0.7945112586021423</v>
+        <v>0.7945112600000001</v>
       </c>
       <c r="AS17" s="3">
-        <v>0.8596585988998413</v>
+        <v>0.8596586000000001</v>
       </c>
       <c r="AT17" s="3">
-        <v>0.6587680578231812</v>
+        <v>0.65876806</v>
       </c>
       <c r="AU17" s="3">
-        <v>-4.819507598876953</v>
+        <v>-4.8195076</v>
       </c>
       <c r="AV17" s="3">
-        <v>98.10469818115234</v>
+        <v>98.10469999999999</v>
       </c>
       <c r="AW17" s="3">
-        <v>9.020400047302246</v>
+        <v>9.0204</v>
       </c>
       <c r="AX17" s="3">
         <v>423.9480000000001</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="AA18" s="3">
-        <v>34.64902496337891</v>
+        <v>34.649025</v>
       </c>
       <c r="AB18" s="3">
-        <v>22.49360275268555</v>
+        <v>22.493603</v>
       </c>
       <c r="AC18" s="3">
-        <v>41.24473571777344</v>
+        <v>41.244736</v>
       </c>
       <c r="AD18" s="3">
         <v>0</v>
@@ -4485,55 +4485,55 @@
         <v>0</v>
       </c>
       <c r="AG18" s="3">
-        <v>0.1139404028654099</v>
+        <v>0.1139404</v>
       </c>
       <c r="AH18" s="3">
-        <v>0.3187094628810883</v>
+        <v>0.31870946</v>
       </c>
       <c r="AI18" s="3">
-        <v>0.8625578880310059</v>
+        <v>0.8625579</v>
       </c>
       <c r="AJ18" s="3">
-        <v>0.07950442284345627</v>
+        <v>0.07950442000000001</v>
       </c>
       <c r="AK18" s="3">
-        <v>0.7735766172409058</v>
+        <v>0.7735765999999999</v>
       </c>
       <c r="AL18" s="3">
-        <v>0.08114465326070786</v>
+        <v>0.08114465</v>
       </c>
       <c r="AM18" s="3">
-        <v>0.3329513669013977</v>
+        <v>0.33295137</v>
       </c>
       <c r="AN18" s="3">
-        <v>0.6034688949584961</v>
+        <v>0.6034689</v>
       </c>
       <c r="AO18" s="3">
-        <v>0.06833945214748383</v>
+        <v>0.06833945</v>
       </c>
       <c r="AP18" s="3">
-        <v>0.9394423365592957</v>
+        <v>0.93944234</v>
       </c>
       <c r="AQ18" s="3">
-        <v>0.9995721578598022</v>
+        <v>0.99957216</v>
       </c>
       <c r="AR18" s="3">
-        <v>0.8234094381332397</v>
+        <v>0.82340944</v>
       </c>
       <c r="AS18" s="3">
-        <v>0.9104534387588501</v>
+        <v>0.9104534399999999</v>
       </c>
       <c r="AT18" s="3">
-        <v>0.8189505338668823</v>
+        <v>0.81895053</v>
       </c>
       <c r="AU18" s="3">
-        <v>-4.971490859985352</v>
+        <v>-4.971491</v>
       </c>
       <c r="AV18" s="3">
-        <v>90.9791259765625</v>
+        <v>90.97912599999999</v>
       </c>
       <c r="AW18" s="3">
-        <v>11.02286148071289</v>
+        <v>11.0228615</v>
       </c>
       <c r="AX18" s="3">
         <v>438.9590000000002</v>
@@ -4601,7 +4601,7 @@
         <v>5.302380392493043</v>
       </c>
       <c r="L19" s="3">
-        <v>1.384457904773821</v>
+        <v>1.384457904773822</v>
       </c>
       <c r="M19" s="3">
         <v>0.5298358977142302</v>
@@ -4625,7 +4625,7 @@
         <v>264.8111481490392</v>
       </c>
       <c r="T19" s="3">
-        <v>3.577063735706287</v>
+        <v>3.577063735706288</v>
       </c>
       <c r="U19" s="3">
         <v>5.654020454746069</v>
@@ -4648,13 +4648,13 @@
         </is>
       </c>
       <c r="AA19" s="3">
-        <v>41.70914840698242</v>
+        <v>41.70915</v>
       </c>
       <c r="AB19" s="3">
-        <v>39.08013153076172</v>
+        <v>39.08013</v>
       </c>
       <c r="AC19" s="3">
-        <v>41.6680908203125</v>
+        <v>41.66809</v>
       </c>
       <c r="AD19" s="3">
         <v>0</v>
@@ -4666,55 +4666,55 @@
         <v>0</v>
       </c>
       <c r="AG19" s="3">
-        <v>0.1859980821609497</v>
+        <v>0.18599808</v>
       </c>
       <c r="AH19" s="3">
-        <v>0.4475581645965576</v>
+        <v>0.44755816</v>
       </c>
       <c r="AI19" s="3">
-        <v>0.8734084963798523</v>
+        <v>0.8734085</v>
       </c>
       <c r="AJ19" s="3">
-        <v>0.07536949217319489</v>
+        <v>0.07536949</v>
       </c>
       <c r="AK19" s="3">
-        <v>0.8774207234382629</v>
+        <v>0.8774207000000001</v>
       </c>
       <c r="AL19" s="3">
-        <v>0.2008223831653595</v>
+        <v>0.20082238</v>
       </c>
       <c r="AM19" s="3">
-        <v>0.4510243535041809</v>
+        <v>0.45102435</v>
       </c>
       <c r="AN19" s="3">
-        <v>0.6147316694259644</v>
+        <v>0.61473167</v>
       </c>
       <c r="AO19" s="3">
-        <v>0.1135449633002281</v>
+        <v>0.11354496</v>
       </c>
       <c r="AP19" s="3">
-        <v>0.9465621709823608</v>
+        <v>0.9465622</v>
       </c>
       <c r="AQ19" s="3">
-        <v>0.999869704246521</v>
+        <v>0.9998697</v>
       </c>
       <c r="AR19" s="3">
-        <v>0.8347463607788086</v>
+        <v>0.83474636</v>
       </c>
       <c r="AS19" s="3">
-        <v>0.9442861676216125</v>
+        <v>0.94428617</v>
       </c>
       <c r="AT19" s="3">
-        <v>0.7134494781494141</v>
+        <v>0.7134495</v>
       </c>
       <c r="AU19" s="3">
-        <v>-4.883634090423584</v>
+        <v>-4.883634</v>
       </c>
       <c r="AV19" s="3">
-        <v>96.95421600341797</v>
+        <v>96.954216</v>
       </c>
       <c r="AW19" s="3">
-        <v>10.06532955169678</v>
+        <v>10.06533</v>
       </c>
       <c r="AX19" s="3">
         <v>403.5300000000001</v>
@@ -4829,13 +4829,13 @@
         </is>
       </c>
       <c r="AA20" s="3">
-        <v>67.29005432128906</v>
+        <v>67.290054</v>
       </c>
       <c r="AB20" s="3">
-        <v>59.42412185668945</v>
+        <v>59.42412</v>
       </c>
       <c r="AC20" s="3">
-        <v>50.19969940185547</v>
+        <v>50.1997</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
@@ -4847,55 +4847,55 @@
         <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0.1062801331281662</v>
+        <v>0.10628013</v>
       </c>
       <c r="AH20" s="3">
-        <v>0.284984678030014</v>
+        <v>0.28498468</v>
       </c>
       <c r="AI20" s="3">
-        <v>0.9137840270996094</v>
+        <v>0.913784</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0.09997934848070145</v>
+        <v>0.09997934999999999</v>
       </c>
       <c r="AK20" s="3">
-        <v>0.6703837513923645</v>
+        <v>0.6703837499999999</v>
       </c>
       <c r="AL20" s="3">
-        <v>0.1034345850348473</v>
+        <v>0.103434585</v>
       </c>
       <c r="AM20" s="3">
-        <v>0.2764445841312408</v>
+        <v>0.27644458</v>
       </c>
       <c r="AN20" s="3">
-        <v>0.5841514468193054</v>
+        <v>0.58415145</v>
       </c>
       <c r="AO20" s="3">
-        <v>0.03564747050404549</v>
+        <v>0.03564747</v>
       </c>
       <c r="AP20" s="3">
-        <v>0.8572244644165039</v>
+        <v>0.85722446</v>
       </c>
       <c r="AQ20" s="3">
-        <v>0.9989715814590454</v>
+        <v>0.9989716</v>
       </c>
       <c r="AR20" s="3">
-        <v>0.8565704226493835</v>
+        <v>0.8565704</v>
       </c>
       <c r="AS20" s="3">
-        <v>0.9090696573257446</v>
+        <v>0.90906966</v>
       </c>
       <c r="AT20" s="3">
-        <v>0.7311879992485046</v>
+        <v>0.7311879999999999</v>
       </c>
       <c r="AU20" s="3">
-        <v>-4.689064025878906</v>
+        <v>-4.689064</v>
       </c>
       <c r="AV20" s="3">
-        <v>102.0556564331055</v>
+        <v>102.05566</v>
       </c>
       <c r="AW20" s="3">
-        <v>5.991437435150146</v>
+        <v>5.9914374</v>
       </c>
       <c r="AX20" s="3">
         <v>413.5250000000001</v>
@@ -5010,13 +5010,13 @@
         </is>
       </c>
       <c r="AA21" s="3">
-        <v>68.97307586669922</v>
+        <v>68.97307600000001</v>
       </c>
       <c r="AB21" s="3">
-        <v>58.76462554931641</v>
+        <v>58.764626</v>
       </c>
       <c r="AC21" s="3">
-        <v>42.25167846679688</v>
+        <v>42.25168</v>
       </c>
       <c r="AD21" s="3">
         <v>0</v>
@@ -5028,55 +5028,55 @@
         <v>0</v>
       </c>
       <c r="AG21" s="3">
-        <v>0.07128484547138214</v>
+        <v>0.071284845</v>
       </c>
       <c r="AH21" s="3">
-        <v>0.2984556555747986</v>
+        <v>0.29845566</v>
       </c>
       <c r="AI21" s="3">
-        <v>0.8959320187568665</v>
+        <v>0.895932</v>
       </c>
       <c r="AJ21" s="3">
-        <v>0.1003864258527756</v>
+        <v>0.100386426</v>
       </c>
       <c r="AK21" s="3">
-        <v>0.6974784135818481</v>
+        <v>0.6974784000000001</v>
       </c>
       <c r="AL21" s="3">
-        <v>0.1394580751657486</v>
+        <v>0.13945808</v>
       </c>
       <c r="AM21" s="3">
-        <v>0.3071840405464172</v>
+        <v>0.30718404</v>
       </c>
       <c r="AN21" s="3">
-        <v>0.5715345144271851</v>
+        <v>0.5715344999999999</v>
       </c>
       <c r="AO21" s="3">
-        <v>0.0425606481730938</v>
+        <v>0.04256065</v>
       </c>
       <c r="AP21" s="3">
-        <v>0.7809053659439087</v>
+        <v>0.78090537</v>
       </c>
       <c r="AQ21" s="3">
-        <v>0.9995959401130676</v>
+        <v>0.99959594</v>
       </c>
       <c r="AR21" s="3">
-        <v>0.868305504322052</v>
+        <v>0.8683055</v>
       </c>
       <c r="AS21" s="3">
-        <v>0.9372184872627258</v>
+        <v>0.9372185</v>
       </c>
       <c r="AT21" s="3">
-        <v>0.6593950986862183</v>
+        <v>0.6593951</v>
       </c>
       <c r="AU21" s="3">
-        <v>-4.684557437896729</v>
+        <v>-4.6845574</v>
       </c>
       <c r="AV21" s="3">
-        <v>100.0310592651367</v>
+        <v>100.03106</v>
       </c>
       <c r="AW21" s="3">
-        <v>5.419719696044922</v>
+        <v>5.4197197</v>
       </c>
       <c r="AX21" s="3">
         <v>413.5250000000001</v>
